--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -39,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,13 +47,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,14 +441,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:40</t>
+          <t>Última actualización: 01:45:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01:45:14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -454,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,14 +528,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:40</t>
+          <t>Última actualización: 01:45:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01:45:14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -502,7 +615,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 00:48:40</t>
+          <t>Última actualización: 01:45:24</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:45:24</t>
+          <t>Última actualización: 02:14:28</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01:45:14</t>
+          <t>02:14:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:45:24</t>
+          <t>Última actualización: 02:14:28</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01:45:14</t>
+          <t>02:14:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03:06</t>
+          <t>02:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:45:24</t>
+          <t>Última actualización: 02:14:28</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:14:28</t>
+          <t>Última actualización: 02:45:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02:14:17</t>
+          <t>02:45:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -496,9 +496,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02:45:21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -528,7 +553,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:14:28</t>
+          <t>Última actualización: 02:45:32</t>
         </is>
       </c>
     </row>
@@ -569,7 +594,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02:14:17</t>
+          <t>02:45:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +608,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -615,7 +640,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:14:28</t>
+          <t>Última actualización: 02:45:32</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -39,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,22 +47,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,91 +432,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:45:32</t>
+          <t>Última actualización: 02:58:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>02:45:21</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>02:58</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215_ALUAR</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>02:45:21</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>03:54</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>69</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
@@ -540,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,66 +467,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:45:32</t>
+          <t>Última actualización: 02:58:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>02:45:21</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>02:58</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215_ALUAR</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
@@ -640,7 +502,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:45:32</t>
+          <t>Última actualización: 02:58:51</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -39,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,13 +47,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,14 +441,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:58:51</t>
+          <t>Última actualización: 03:49:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>03:49:09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -454,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,14 +528,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:58:51</t>
+          <t>Última actualización: 03:49:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>03:49:09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -502,7 +615,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 02:58:51</t>
+          <t>Última actualización: 03:49:19</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:49:19</t>
+          <t>Última actualización: 04:31:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03:49:09</t>
+          <t>04:31:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -496,9 +496,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>04:31:28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>04:31:28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -528,7 +578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:49:19</t>
+          <t>Última actualización: 04:31:38</t>
         </is>
       </c>
     </row>
@@ -569,7 +619,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03:49:09</t>
+          <t>04:31:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +633,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -602,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,14 +665,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:49:19</t>
+          <t>Última actualización: 04:31:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>04:31:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>98</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:31:38</t>
+          <t>Última actualización: 04:55:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,73 +482,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04:31:28</t>
+          <t>04:55:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04:46</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>04:31:28</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>05:36</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>04:31:28</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>06:04</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>93</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -565,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,66 +528,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:31:38</t>
+          <t>Última actualización: 04:55:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>04:31:28</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>04:46</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
@@ -665,7 +563,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:31:38</t>
+          <t>Última actualización: 04:55:31</t>
         </is>
       </c>
     </row>
@@ -706,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04:31:38</t>
+          <t>04:55:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -720,7 +618,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:31</t>
+          <t>Última actualización: 05:40:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 4 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04:55:20</t>
+          <t>05:40:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,9 +496,84 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05:40:14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05:40:14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>05:40:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -528,7 +603,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:31</t>
+          <t>Última actualización: 05:40:24</t>
         </is>
       </c>
     </row>
@@ -550,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,14 +638,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:31</t>
+          <t>Última actualización: 05:40:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -604,7 +679,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04:55:31</t>
+          <t>05:40:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,9 +693,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05:40:24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:40:24</t>
+          <t>Última actualización: 06:03:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 4 filas únicas</t>
+          <t>Ejecuciones: 8 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05:40:14</t>
+          <t>06:03:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05:40:14</t>
+          <t>06:03:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>86_EST CHICA-ESC AGRARIA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05:40:14</t>
+          <t>06:03:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,12 +557,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05:40:14</t>
+          <t>06:03:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -571,9 +571,109 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>06:03:41</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>06:03:41</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>78</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06:03:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>88</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06:03:41</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>96</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -590,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,14 +703,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:40:24</t>
+          <t>Última actualización: 06:03:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06:03:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -638,7 +790,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:40:24</t>
+          <t>Última actualización: 06:03:52</t>
         </is>
       </c>
     </row>
@@ -679,12 +831,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05:40:24</t>
+          <t>06:03:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -693,7 +845,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -704,12 +856,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05:40:24</t>
+          <t>06:03:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -718,7 +870,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:03:52</t>
+          <t>Última actualización: 06:44:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 8 filas únicas</t>
+          <t>Ejecuciones: 15 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>86_EST CHICA-ESC AGRARIA</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,23 +657,198 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>47</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>47</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>52</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>07:39</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>10_OLMOS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>96</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D18" t="n">
+        <v>55</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>79</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>99</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -690,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,14 +878,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:03:52</t>
+          <t>Última actualización: 06:44:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -744,7 +919,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:03:41</t>
+          <t>06:44:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -758,9 +933,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06:44:36</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -790,7 +990,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:03:52</t>
+          <t>Última actualización: 06:44:47</t>
         </is>
       </c>
     </row>
@@ -831,21 +1031,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:03:51</t>
+          <t>06:44:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215B_LP-P MOR-1 Y 57</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -856,21 +1056,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06:03:51</t>
+          <t>06:44:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-1 Y 57</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:47</t>
+          <t>Última actualización: 07:00:12</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:04</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:47</t>
+          <t>Última actualización: 07:00:12</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06:44:36</t>
+          <t>07:00:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,14 +990,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:44:47</t>
+          <t>Última actualización: 07:00:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1031,21 +1031,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06:44:47</t>
+          <t>07:00:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-1 Y 57</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1056,23 +1056,48 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06:44:47</t>
+          <t>07:00:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07:00:12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:00:12</t>
+          <t>Última actualización: 07:38:51</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,12 +532,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,12 +557,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,12 +607,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:00:12</t>
+          <t>Última actualización: 07:38:51</t>
         </is>
       </c>
     </row>
@@ -919,21 +919,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -944,21 +944,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:00:01</t>
+          <t>07:38:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:00:12</t>
+          <t>Última actualización: 07:38:51</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:00:12</t>
+          <t>07:38:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1056,12 +1056,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:00:07</t>
+          <t>07:38:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1081,12 +1081,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07:00:12</t>
+          <t>07:38:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:38:51</t>
+          <t>Última actualización: 07:59:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 15 filas únicas</t>
+          <t>Ejecuciones: 23 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>215B_EL PATO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,23 +832,223 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>56</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>62</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>09:01</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>215A_EL PATO</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D22" t="n">
+        <v>63</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>83</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>84</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>85</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>07:58:51</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>93</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -878,7 +1078,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:38:51</t>
+          <t>Última actualización: 07:59:01</t>
         </is>
       </c>
     </row>
@@ -919,7 +1119,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -933,7 +1133,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -944,7 +1144,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:38:40</t>
+          <t>07:58:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -958,7 +1158,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -977,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,14 +1190,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:38:51</t>
+          <t>Última actualización: 07:59:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1231,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:38:51</t>
+          <t>07:59:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1045,59 +1245,9 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>07:38:46</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>L6203</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>07:38:51</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215A_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>61</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:59:01</t>
+          <t>Última actualización: 08:30:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 23 filas únicas</t>
+          <t>Ejecuciones: 22 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,12 +482,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1021,34 +1021,9 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>07:58:51</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>93</v>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1065,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,14 +1053,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:59:01</t>
+          <t>Última actualización: 08:30:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1119,48 +1094,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:58:51</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_EL PATO</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>07:58:51</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>63</v>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1177,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,14 +1140,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:59:01</t>
+          <t>Última actualización: 08:30:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1181,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07:59:01</t>
+          <t>08:30:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1245,9 +1195,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>08:30:28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215D_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>48</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08:30:33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:30:33</t>
+          <t>Última actualización: 08:48:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 22 filas únicas</t>
+          <t>Ejecuciones: 24 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,23 +1007,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08:48:13</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>95</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08:48:13</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>99</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1040,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,14 +1103,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:30:33</t>
+          <t>Última actualización: 08:48:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 3 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1094,23 +1144,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:48:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>08:48:13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>09:42</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>215C_EL PATO</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>72</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08:48:13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>99</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1140,7 +1240,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:30:33</t>
+          <t>Última actualización: 08:48:24</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1281,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:30:33</t>
+          <t>08:48:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1195,7 +1295,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1206,12 +1306,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08:30:28</t>
+          <t>08:48:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1220,7 +1320,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1231,7 +1331,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08:30:33</t>
+          <t>08:48:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1345,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:48:24</t>
+          <t>Última actualización: 10:01:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 24 filas únicas</t>
+          <t>Ejecuciones: 25 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,17 +507,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215A_EL PATO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>215C_EL PATO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1057,23 +1057,48 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10:01:28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>94</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1090,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,14 +1128,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:48:24</t>
+          <t>Última actualización: 10:01:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1169,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1158,7 +1183,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1169,12 +1194,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08:48:13</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1183,34 +1208,9 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>08:48:13</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>99</v>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1240,7 +1240,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:48:24</t>
+          <t>Última actualización: 10:01:39</t>
         </is>
       </c>
     </row>
@@ -1281,21 +1281,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08:48:24</t>
+          <t>10:01:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215B_LP-P MOR-40 Y 115</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1306,50 +1306,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08:48:18</t>
+          <t>10:01:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215D_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08:48:24</t>
+          <t>10:01:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:01:39</t>
+          <t>Última actualización: 10:53:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 25 filas únicas</t>
+          <t>Ejecuciones: 21 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>86_EST CHICA-ESC AGRARIA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>81_EL PELIGRO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>215A_EL PATO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,21 +882,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -907,21 +907,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>215C_EL PATO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -957,21 +957,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -982,123 +982,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10:01:28</t>
+          <t>10:53:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>71</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>80</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>81_EL PELIGRO</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>91</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>11_ETCHEVERRY</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>94</v>
-      </c>
-      <c r="E30" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1115,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,91 +1028,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:01:39</t>
+          <t>Última actualización: 10:53:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Scrap</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hora_Llegada</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Línea</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Minutos</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>215A_EL PATO</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10:01:28</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215C_EL PATO</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>61</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LP1912</t>
+          <t>Ejecuciones: 0 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,14 +1063,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:01:39</t>
+          <t>Última actualización: 10:53:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 3 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1281,37 +1104,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10:01:39</t>
+          <t>10:53:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215B_LP-P MOR-40 Y 115</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10:01:39</t>
+          <t>10:53:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1320,36 +1143,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10:01:33</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>73</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:18</t>
+          <t>Última actualización: 11:33:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 21 filas únicas</t>
+          <t>Ejecuciones: 17 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16_P MOR-167 Y 521</t>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>86_EST CHICA-ESC AGRARIA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,12 +657,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>81_EL PELIGRO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>17_179 Y 38</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,123 +882,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10:53:08</t>
+          <t>11:33:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10:53:08</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>10_OLMOS</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>78</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10:53:08</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>88</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10:53:08</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>14_ABASTO</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>89</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10:53:08</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>91</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1028,7 +928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:18</t>
+          <t>Última actualización: 11:33:48</t>
         </is>
       </c>
     </row>
@@ -1063,7 +963,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:18</t>
+          <t>Última actualización: 11:33:48</t>
         </is>
       </c>
     </row>
@@ -1104,50 +1004,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10:53:13</t>
+          <t>11:33:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>215C_LA PLATA</t>
+          <t>215A_LA PLATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>L6203</t>
+          <t>L6173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10:53:18</t>
+          <t>11:33:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>215A_LA PLATA</t>
+          <t>215C_LA PLATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>L6173</t>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:33:48</t>
+          <t>Última actualización: 12:00:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 17 filas únicas</t>
+          <t>Ejecuciones: 20 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,21 +532,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>84_COLONIA URQUIZA-ESC 49</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>27_EL RETIRO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>17_179 Y 38</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17_179 Y 38</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,23 +882,98 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11:33:37</t>
+          <t>12:00:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12:00:32</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>89</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12:00:32</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>94</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12:00:32</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>96</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -928,7 +1003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:33:48</t>
+          <t>Última actualización: 12:00:42</t>
         </is>
       </c>
     </row>
@@ -963,7 +1038,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:33:48</t>
+          <t>Última actualización: 12:00:42</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1079,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11:33:48</t>
+          <t>12:00:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1018,7 +1093,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1029,12 +1104,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11:33:43</t>
+          <t>12:00:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1043,7 +1118,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:00:42</t>
+          <t>Última actualización: 12:44:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 20 filas únicas</t>
+          <t>Ejecuciones: 17 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,12 +532,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,21 +557,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26_HERNANDEZ</t>
+          <t>16_P MOR-SANTA ANA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27_EL RETIRO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17_179 Y 38</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11_ETCHEVERRY</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,21 +757,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -857,21 +857,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -882,98 +882,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12:00:32</t>
+          <t>12:43:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>12:00:32</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>17_ROMERO</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>89</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12:00:32</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>23_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>94</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12:00:32</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>15_ABASTO</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>96</v>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1003,7 +928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:00:42</t>
+          <t>Última actualización: 12:44:06</t>
         </is>
       </c>
     </row>
@@ -1025,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,14 +963,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:00:42</t>
+          <t>Última actualización: 12:44:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Ejecuciones: 1 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1004,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:00:42</t>
+          <t>12:44:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,36 +1018,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>L6173</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>12:00:37</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>215C_LA PLATA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:44:06</t>
+          <t>Última actualización: 13:01:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 17 filas únicas</t>
+          <t>Ejecuciones: 15 filas únicas</t>
         </is>
       </c>
     </row>
@@ -482,21 +482,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16_SANTA ANA</t>
+          <t>14_ABASTO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,21 +507,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -532,12 +532,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -557,17 +557,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -582,21 +582,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,21 +607,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16_P MOR-SANTA ANA</t>
+          <t>10_OLMOS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -632,21 +632,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,21 +657,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14_ABASTO</t>
+          <t>15_ABASTO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -682,21 +682,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10_OLMOS</t>
+          <t>16_SANTA ANA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -707,21 +707,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>17_ROMERO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15_ABASTO</t>
+          <t>16_P MOR-167 Y 521</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -757,12 +757,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -782,21 +782,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>23_HERNANDEZ</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17_ROMERO</t>
+          <t>26_HERNANDEZ</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -832,73 +832,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12:43:55</t>
+          <t>13:01:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23_HERNANDEZ</t>
+          <t>11_ETCHEVERRY</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>12:43:55</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>16_SANTA ANA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>94</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LP1912</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12:43:55</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>26_HERNANDEZ</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>97</v>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -928,7 +878,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:44:06</t>
+          <t>Última actualización: 13:01:27</t>
         </is>
       </c>
     </row>
@@ -950,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,14 +913,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:44:06</t>
+          <t>Última actualización: 13:01:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 1 filas únicas</t>
+          <t>Ejecuciones: 2 filas únicas</t>
         </is>
       </c>
     </row>
@@ -1004,23 +954,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12:44:06</t>
+          <t>13:01:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>13:01:27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>14:09</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>215A_LA PLATA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>85</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="n">
+        <v>68</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LP1912" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LP1912-215" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="6203-6173" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LP1912" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LP1912-215" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6203-6173" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:01:27</t>
+          <t>Última actualización: 19:42:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 15 filas únicas</t>
+          <t>Total filas: 34</t>
         </is>
       </c>
     </row>
@@ -849,6 +849,481 @@
         <v>90</v>
       </c>
       <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>27</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>29</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>39</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>41</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>62</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>64</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>70</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>75</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>82</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>86</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>99</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -865,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,14 +1353,91 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:01:27</t>
+          <t>Última actualización: 19:42:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 0 filas únicas</t>
+          <t>Total filas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>19:42:45</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>86</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -900,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,14 +1465,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:01:27</t>
+          <t>Última actualización: 19:42:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ejecuciones: 2 filas únicas</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -996,6 +1548,56 @@
         <v>68</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>19:42:49</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>19:42:52</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>57</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:42:52</t>
+          <t>Última actualización: 19:48:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 34</t>
+          <t>Total filas: 42</t>
         </is>
       </c>
     </row>
@@ -1324,6 +1324,206 @@
         <v>99</v>
       </c>
       <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>25</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>35</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>36</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>59</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>65</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>95</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>95</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1340,7 +1540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1353,14 +1553,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:42:52</t>
+          <t>Última actualización: 19:48:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -1436,6 +1636,31 @@
         <v>86</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>19:48:13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1465,7 +1690,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:42:52</t>
+          <t>Última actualización: 19:48:19</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:48:19</t>
+          <t>Última actualización: 20:21:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 42</t>
+          <t>Total filas: 49</t>
         </is>
       </c>
     </row>
@@ -1524,6 +1524,181 @@
         <v>95</v>
       </c>
       <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>55</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>71</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>85</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>86</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>88</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>92</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1540,7 +1715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,14 +1728,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:48:19</t>
+          <t>Última actualización: 20:21:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1661,6 +1836,31 @@
         <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20:21:45</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>86</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1677,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1690,14 +1890,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:48:19</t>
+          <t>Última actualización: 20:21:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -1825,6 +2025,31 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20:21:48</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>67</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:21:51</t>
+          <t>Última actualización: 20:42:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 49</t>
+          <t>Total filas: 57</t>
         </is>
       </c>
     </row>
@@ -1699,6 +1699,206 @@
         <v>92</v>
       </c>
       <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>35</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>51</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>86</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>86</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>87</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20:42:06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>99</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1728,7 +1928,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:21:51</t>
+          <t>Última actualización: 20:42:12</t>
         </is>
       </c>
     </row>
@@ -1877,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,14 +2090,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:21:51</t>
+          <t>Última actualización: 20:42:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -2050,6 +2250,81 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20:42:09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>47</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20:42:12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>83</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20:42:12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>99</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:42:12</t>
+          <t>Última actualización: 20:54:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 57</t>
+          <t>Total filas: 62</t>
         </is>
       </c>
     </row>
@@ -1899,6 +1899,131 @@
         <v>99</v>
       </c>
       <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20:54:03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20:54:03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>85</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20:54:03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>88</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20:54:03</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>89</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20:54:03</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>94</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1928,7 +2053,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:42:12</t>
+          <t>Última actualización: 20:54:09</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2215,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:42:12</t>
+          <t>Última actualización: 20:54:09</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-08.xlsx
+++ b/horarios-141-2026-01-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:54:09</t>
+          <t>Última actualización: 23:01:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 62</t>
+          <t>Total filas: 66</t>
         </is>
       </c>
     </row>
@@ -2024,6 +2024,106 @@
         <v>94</v>
       </c>
       <c r="E67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>23:01:25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>23:01:25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23:12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>23:01:25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>45</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>23:01:25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>51</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2040,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,14 +2153,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:54:09</t>
+          <t>Última actualización: 23:01:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -2186,6 +2286,31 @@
         <v>86</v>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>23:01:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>51</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2202,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2215,14 +2340,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:54:09</t>
+          <t>Última actualización: 23:01:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -2448,6 +2573,31 @@
         <v>99</v>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>23:01:37</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>
